--- a/연구코드/results/feature_selection/merged/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/merged/step2_vif.xlsx
@@ -519,7 +519,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1475.943670683168</v>
+        <v>1475.94367068341</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -543,7 +543,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>404.7850590942015</v>
+        <v>404.7850590942197</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>202.4128183590911</v>
+        <v>202.4128183591183</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>194.5523729317617</v>
+        <v>194.5523729319676</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -591,7 +591,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>129.2392535271388</v>
+        <v>129.2392535271407</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -607,7 +607,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>105.6837534342637</v>
+        <v>105.6837534342649</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -615,7 +615,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>93.02101771977938</v>
+        <v>93.02101771978033</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>84.08008667701968</v>
+        <v>84.08008667705971</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -631,7 +631,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>83.57537974870375</v>
+        <v>83.57537974870453</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -639,7 +639,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>63.27955130643879</v>
+        <v>63.27955130643924</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -647,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>56.61203709648511</v>
+        <v>56.61203709648582</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -679,7 +679,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>35.35808744079256</v>
+        <v>35.35808744079576</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -687,7 +687,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>31.18565164428958</v>
+        <v>31.18565164429001</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -695,7 +695,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>28.00914104991081</v>
+        <v>28.00914104991125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -703,7 +703,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>27.05486126583222</v>
+        <v>27.05486126583278</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -719,7 +719,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>21.32480698376821</v>
+        <v>21.32480698377377</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -727,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>20.88415948798974</v>
+        <v>20.88415948799841</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -735,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>19.12110947388943</v>
+        <v>19.12110947388939</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -743,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>18.67727752188462</v>
+        <v>18.67727752188497</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>18.39245377293392</v>
+        <v>18.39245377293771</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -767,7 +767,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>14.48594287431152</v>
+        <v>14.48594287431166</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -783,7 +783,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>11.73411018848921</v>
+        <v>11.73411018848946</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -815,7 +815,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>7.968052388644953</v>
+        <v>7.968052388645115</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -823,7 +823,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>7.00616397049654</v>
+        <v>7.006163970497221</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -831,7 +831,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>6.118056739187805</v>
+        <v>6.118056739187826</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -839,7 +839,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>4.74652599951668</v>
+        <v>4.7465259995171</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -847,7 +847,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>3.690056290732489</v>
+        <v>3.690056290732488</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/merged/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/merged/step2_vif.xlsx
@@ -519,7 +519,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1475.94367068341</v>
+        <v>1475.943670683168</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -543,7 +543,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>404.7850590942197</v>
+        <v>404.7850590942015</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>202.4128183591183</v>
+        <v>202.4128183590911</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>194.5523729319676</v>
+        <v>194.5523729317617</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -591,7 +591,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>129.2392535271407</v>
+        <v>129.2392535271388</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -607,7 +607,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>105.6837534342649</v>
+        <v>105.6837534342637</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -615,7 +615,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>93.02101771978033</v>
+        <v>93.02101771977938</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>84.08008667705971</v>
+        <v>84.08008667701968</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -631,7 +631,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>83.57537974870453</v>
+        <v>83.57537974870375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -639,7 +639,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>63.27955130643924</v>
+        <v>63.27955130643879</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -647,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>56.61203709648582</v>
+        <v>56.61203709648511</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -679,7 +679,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>35.35808744079576</v>
+        <v>35.35808744079256</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -687,7 +687,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>31.18565164429001</v>
+        <v>31.18565164428958</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -695,7 +695,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>28.00914104991125</v>
+        <v>28.00914104991081</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -703,7 +703,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>27.05486126583278</v>
+        <v>27.05486126583222</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -719,7 +719,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>21.32480698377377</v>
+        <v>21.32480698376821</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -727,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>20.88415948799841</v>
+        <v>20.88415948798974</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -735,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>19.12110947388939</v>
+        <v>19.12110947388943</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -743,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>18.67727752188497</v>
+        <v>18.67727752188462</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>18.39245377293771</v>
+        <v>18.39245377293392</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -767,7 +767,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>14.48594287431166</v>
+        <v>14.48594287431152</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -783,7 +783,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>11.73411018848946</v>
+        <v>11.73411018848921</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -815,7 +815,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>7.968052388645115</v>
+        <v>7.968052388644953</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -823,7 +823,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>7.006163970497221</v>
+        <v>7.00616397049654</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -831,7 +831,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>6.118056739187826</v>
+        <v>6.118056739187805</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -839,7 +839,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>4.7465259995171</v>
+        <v>4.74652599951668</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -847,7 +847,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>3.690056290732488</v>
+        <v>3.690056290732489</v>
       </c>
     </row>
   </sheetData>
